--- a/data/trans_orig/P16A02-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A02-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2007</t>
+          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43830</t>
+          <t>46368</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>72862</t>
+          <t>73120</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>49035</t>
+          <t>48677</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>76894</t>
+          <t>76951</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>102477</t>
+          <t>101389</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>141412</t>
+          <t>142275</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,23%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>400914</t>
+          <t>400656</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>429946</t>
+          <t>427408</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>229786</t>
+          <t>229729</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>257645</t>
+          <t>258003</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>639045</t>
+          <t>638182</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>677980</t>
+          <t>679068</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>87,01%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44316</t>
+          <t>44194</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72880</t>
+          <t>73772</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67987</t>
+          <t>68905</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>103315</t>
+          <t>101209</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>120982</t>
+          <t>122227</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>164739</t>
+          <t>163335</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,11%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>294054</t>
+          <t>293162</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>322618</t>
+          <t>322740</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>268550</t>
+          <t>270656</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>303878</t>
+          <t>302960</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>574060</t>
+          <t>575464</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>617817</t>
+          <t>616572</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>83,46%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55030</t>
+          <t>54760</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>85198</t>
+          <t>84739</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29405</t>
+          <t>29488</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50595</t>
+          <t>52189</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>92032</t>
+          <t>90691</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>129287</t>
+          <t>129407</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,22%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>457191</t>
+          <t>457650</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>487359</t>
+          <t>487629</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>117187</t>
+          <t>115593</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>138377</t>
+          <t>138294</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>580884</t>
+          <t>580764</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>618139</t>
+          <t>619480</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,23%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>177392</t>
+          <t>178429</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>229260</t>
+          <t>229994</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>137122</t>
+          <t>132703</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>178702</t>
+          <t>176676</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>322634</t>
+          <t>323638</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>390280</t>
+          <t>394746</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,22%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1009074</t>
+          <t>1008340</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1060942</t>
+          <t>1059905</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>535583</t>
+          <t>537609</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>577163</t>
+          <t>581582</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1562340</t>
+          <t>1557874</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1629986</t>
+          <t>1628982</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,43%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37540</t>
+          <t>37080</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61901</t>
+          <t>62618</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>133541</t>
+          <t>131848</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>175105</t>
+          <t>174746</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>180495</t>
+          <t>179672</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>228838</t>
+          <t>232771</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,35%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>287636</t>
+          <t>286919</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>311997</t>
+          <t>312457</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>393647</t>
+          <t>394006</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>435211</t>
+          <t>436904</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>689451</t>
+          <t>685518</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>737794</t>
+          <t>738617</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,43%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11627</t>
+          <t>11656</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27883</t>
+          <t>27200</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>279175</t>
+          <t>281788</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>341506</t>
+          <t>343036</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>296512</t>
+          <t>298510</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>362706</t>
+          <t>362198</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,41%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>270318</t>
+          <t>271001</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>286574</t>
+          <t>286545</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>907254</t>
+          <t>905724</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>969585</t>
+          <t>966972</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1184254</t>
+          <t>1184762</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1250448</t>
+          <t>1248450</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,7%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>415562</t>
+          <t>415575</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>496675</t>
+          <t>493671</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>754211</t>
+          <t>758649</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>853079</t>
+          <t>858134</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1197169</t>
+          <t>1197307</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1322679</t>
+          <t>1326977</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,96%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2772497</t>
+          <t>2775501</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2853610</t>
+          <t>2853597</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2525045</t>
+          <t>2519990</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2623913</t>
+          <t>2619475</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5324617</t>
+          <t>5320319</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5450127</t>
+          <t>5449989</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2012</t>
+          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2012 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43449</t>
+          <t>42593</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>74901</t>
+          <t>72608</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>65859</t>
+          <t>65759</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>98702</t>
+          <t>98580</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>116703</t>
+          <t>117797</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>160446</t>
+          <t>159131</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,17%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>362310</t>
+          <t>364603</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>393762</t>
+          <t>394618</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>215752</t>
+          <t>215874</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>248595</t>
+          <t>248695</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>591219</t>
+          <t>592534</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>634962</t>
+          <t>633868</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,33%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59446</t>
+          <t>60203</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>93284</t>
+          <t>94021</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>91415</t>
+          <t>91165</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>130630</t>
+          <t>126353</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>161414</t>
+          <t>159076</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>212761</t>
+          <t>208702</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>27,68%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>323734</t>
+          <t>322997</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>357572</t>
+          <t>356815</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>206404</t>
+          <t>210681</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>245619</t>
+          <t>245869</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>541291</t>
+          <t>545350</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>592638</t>
+          <t>594976</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,9%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>111977</t>
+          <t>111675</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>155512</t>
+          <t>154987</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56643</t>
+          <t>58597</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88402</t>
+          <t>88798</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>181473</t>
+          <t>179757</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>233978</t>
+          <t>233915</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,39%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>472817</t>
+          <t>473342</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>516352</t>
+          <t>516654</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>169536</t>
+          <t>169140</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>201295</t>
+          <t>199341</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>652289</t>
+          <t>652352</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>704794</t>
+          <t>706510</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,72%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>208872</t>
+          <t>209181</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>267875</t>
+          <t>265148</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>204082</t>
+          <t>205966</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>257841</t>
+          <t>255148</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>425864</t>
+          <t>431849</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>505747</t>
+          <t>505289</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,26%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>889440</t>
+          <t>892167</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>948443</t>
+          <t>948134</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>508816</t>
+          <t>511509</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>562575</t>
+          <t>560691</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1418226</t>
+          <t>1418684</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1498109</t>
+          <t>1492124</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>77,55%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>73761</t>
+          <t>74729</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>109398</t>
+          <t>110040</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>265071</t>
+          <t>264192</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>318172</t>
+          <t>320390</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>350460</t>
+          <t>348663</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>419760</t>
+          <t>415332</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,68%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>401198</t>
+          <t>400556</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>436835</t>
+          <t>435867</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>442315</t>
+          <t>440097</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>495416</t>
+          <t>496295</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>851324</t>
+          <t>855752</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>920624</t>
+          <t>922421</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,57%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12270</t>
+          <t>12292</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28577</t>
+          <t>27720</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>368901</t>
+          <t>368787</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>432898</t>
+          <t>435593</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>388534</t>
+          <t>386883</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>455611</t>
+          <t>457993</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,38%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>237264</t>
+          <t>238121</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>253571</t>
+          <t>253549</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>673342</t>
+          <t>670647</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>737339</t>
+          <t>737453</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>916470</t>
+          <t>914088</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>983547</t>
+          <t>985198</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,8%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>565369</t>
+          <t>565363</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>658184</t>
+          <t>658090</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1128697</t>
+          <t>1125788</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1247306</t>
+          <t>1243950</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1716913</t>
+          <t>1721812</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1867910</t>
+          <t>1870194</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,87%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2758126</t>
+          <t>2758220</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2850941</t>
+          <t>2850947</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2295505</t>
+          <t>2298861</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2414114</t>
+          <t>2417023</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5091211</t>
+          <t>5088927</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5242208</t>
+          <t>5237309</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,26%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2016</t>
+          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>69172</t>
+          <t>68462</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>102297</t>
+          <t>102693</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>66905</t>
+          <t>67348</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>98632</t>
+          <t>98345</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>146489</t>
+          <t>141390</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>190986</t>
+          <t>189395</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,4%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>326795</t>
+          <t>326399</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>359920</t>
+          <t>360630</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>248423</t>
+          <t>248710</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>280150</t>
+          <t>279707</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>585161</t>
+          <t>586752</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>629658</t>
+          <t>634757</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,78%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52020</t>
+          <t>52927</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>81279</t>
+          <t>82256</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>79418</t>
+          <t>80776</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>114113</t>
+          <t>114848</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>139566</t>
+          <t>139244</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>186458</t>
+          <t>186305</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,86%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>295948</t>
+          <t>294971</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>325207</t>
+          <t>324300</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>258160</t>
+          <t>257425</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>292855</t>
+          <t>291497</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>563042</t>
+          <t>563195</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>609934</t>
+          <t>610256</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,42%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>87166</t>
+          <t>86964</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>123062</t>
+          <t>123248</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47355</t>
+          <t>46897</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72936</t>
+          <t>73681</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>141956</t>
+          <t>142797</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>187586</t>
+          <t>188660</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,42%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>398852</t>
+          <t>398666</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>434748</t>
+          <t>434950</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>93187</t>
+          <t>92442</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>118768</t>
+          <t>119226</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>500450</t>
+          <t>499376</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>546080</t>
+          <t>545239</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>79,25%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>201864</t>
+          <t>200283</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>256003</t>
+          <t>257768</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>211267</t>
+          <t>213813</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>264464</t>
+          <t>264417</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>429785</t>
+          <t>429790</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>505479</t>
+          <t>509965</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,81%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>893635</t>
+          <t>891870</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>947774</t>
+          <t>949355</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>561412</t>
+          <t>561459</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>614609</t>
+          <t>612063</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1470035</t>
+          <t>1465549</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1545729</t>
+          <t>1545724</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>97421</t>
+          <t>97368</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>136942</t>
+          <t>137398</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>242250</t>
+          <t>240520</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>295250</t>
+          <t>291230</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>351143</t>
+          <t>346793</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>422304</t>
+          <t>414600</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,51%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>483764</t>
+          <t>483308</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>523285</t>
+          <t>523338</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>442994</t>
+          <t>447014</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>495994</t>
+          <t>497724</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>936646</t>
+          <t>944350</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1007807</t>
+          <t>1012157</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,48%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26550</t>
+          <t>26618</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50158</t>
+          <t>51518</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>319826</t>
+          <t>325245</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>385891</t>
+          <t>388116</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>356537</t>
+          <t>361204</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>429399</t>
+          <t>428615</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,3%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>236987</t>
+          <t>235627</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260595</t>
+          <t>260527</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>696134</t>
+          <t>693909</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>762199</t>
+          <t>756780</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>939771</t>
+          <t>940555</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1012633</t>
+          <t>1007966</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>73,62%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>596353</t>
+          <t>590418</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>684670</t>
+          <t>681638</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1038094</t>
+          <t>1038332</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1155304</t>
+          <t>1157172</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1659087</t>
+          <t>1663220</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1805842</t>
+          <t>1808228</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,14%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2701052</t>
+          <t>2704084</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2789369</t>
+          <t>2795304</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2376292</t>
+          <t>2374424</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2493502</t>
+          <t>2493264</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5111476</t>
+          <t>5109090</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5258231</t>
+          <t>5254098</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>75,96%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2023</t>
+          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2023 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>77566</t>
+          <t>76905</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>114408</t>
+          <t>115335</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>126811</t>
+          <t>125733</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>161144</t>
+          <t>160615</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>214487</t>
+          <t>213122</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>262240</t>
+          <t>264221</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,73%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>390804</t>
+          <t>389877</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>427646</t>
+          <t>428307</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>286323</t>
+          <t>286852</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>320656</t>
+          <t>321734</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>690439</t>
+          <t>688458</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>738192</t>
+          <t>739557</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,63%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>76378</t>
+          <t>76881</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>110996</t>
+          <t>111643</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>106634</t>
+          <t>106927</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>136761</t>
+          <t>138636</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>192688</t>
+          <t>193854</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>240132</t>
+          <t>238291</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,54%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>341217</t>
+          <t>340570</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>375835</t>
+          <t>375332</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>245819</t>
+          <t>243944</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>275946</t>
+          <t>275653</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>594661</t>
+          <t>596502</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>642105</t>
+          <t>640939</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>76,78%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42529</t>
+          <t>47991</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>194014</t>
+          <t>195026</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>68711</t>
+          <t>68438</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89533</t>
+          <t>89012</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>85162</t>
+          <t>92097</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>287618</t>
+          <t>285635</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,2%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>474250</t>
+          <t>473238</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>625735</t>
+          <t>620273</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>77378</t>
+          <t>77899</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>98200</t>
+          <t>98473</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>547557</t>
+          <t>549540</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>750013</t>
+          <t>743078</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>88,97%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>267019</t>
+          <t>266931</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>327211</t>
+          <t>330128</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>370988</t>
+          <t>369053</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>726877</t>
+          <t>695500</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>649331</t>
+          <t>650127</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1130587</t>
+          <t>1195798</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>59,41%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>707608</t>
+          <t>704691</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>767800</t>
+          <t>767888</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>251217</t>
+          <t>282594</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>607106</t>
+          <t>609041</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>882325</t>
+          <t>817114</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1363581</t>
+          <t>1362785</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>67,7%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>108263</t>
+          <t>110249</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>148633</t>
+          <t>150591</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>262418</t>
+          <t>278410</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>415123</t>
+          <t>418190</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>407281</t>
+          <t>400405</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>542961</t>
+          <t>543791</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,38%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>326413</t>
+          <t>324455</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>366783</t>
+          <t>364797</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>423873</t>
+          <t>420806</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>576578</t>
+          <t>560586</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>771080</t>
+          <t>770250</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>906760</t>
+          <t>913636</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>69,53%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17169</t>
+          <t>17749</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>56444</t>
+          <t>55648</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>269334</t>
+          <t>269898</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>317763</t>
+          <t>316226</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>293942</t>
+          <t>292633</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>356244</t>
+          <t>354209</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,4%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>184063</t>
+          <t>184859</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>223338</t>
+          <t>222758</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>442389</t>
+          <t>443926</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>490818</t>
+          <t>490254</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>644415</t>
+          <t>646450</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>706717</t>
+          <t>708026</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,76%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>585173</t>
+          <t>597696</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>841542</t>
+          <t>842135</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1356466</t>
+          <t>1356729</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1891783</t>
+          <t>1900198</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2052127</t>
+          <t>2029388</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2663134</t>
+          <t>2720438</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>39,14%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2534518</t>
+          <t>2533925</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2790887</t>
+          <t>2778364</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1682416</t>
+          <t>1674001</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2217733</t>
+          <t>2217470</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4287126</t>
+          <t>4229822</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4898133</t>
+          <t>4920872</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>70,8%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A02-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A02-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>46368</t>
+          <t>45337</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>73120</t>
+          <t>72810</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>48677</t>
+          <t>49947</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>76951</t>
+          <t>77605</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>101389</t>
+          <t>101106</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>142275</t>
+          <t>143576</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>400656</t>
+          <t>400966</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>427408</t>
+          <t>428439</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>229729</t>
+          <t>229075</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>258003</t>
+          <t>256733</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>638182</t>
+          <t>636881</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>679068</t>
+          <t>679351</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>87,05%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44194</t>
+          <t>45208</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73772</t>
+          <t>73681</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>68905</t>
+          <t>68434</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>101209</t>
+          <t>101313</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>122227</t>
+          <t>120500</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>163335</t>
+          <t>164620</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>293162</t>
+          <t>293253</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>322740</t>
+          <t>321726</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>270656</t>
+          <t>270552</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>302960</t>
+          <t>303431</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>575464</t>
+          <t>574179</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>616572</t>
+          <t>618299</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,69%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54760</t>
+          <t>56312</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>84739</t>
+          <t>86001</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29488</t>
+          <t>28942</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52189</t>
+          <t>51237</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>90691</t>
+          <t>91922</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>129407</t>
+          <t>130389</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,36%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>457650</t>
+          <t>456388</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>487629</t>
+          <t>486077</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>115593</t>
+          <t>116545</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>138294</t>
+          <t>138840</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>580764</t>
+          <t>579782</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>619480</t>
+          <t>618249</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,06%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>178429</t>
+          <t>176971</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>229994</t>
+          <t>227684</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>132703</t>
+          <t>131820</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>176676</t>
+          <t>177438</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>323638</t>
+          <t>328190</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>394746</t>
+          <t>392470</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,1%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1008340</t>
+          <t>1010650</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1059905</t>
+          <t>1061363</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>537609</t>
+          <t>536847</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>581582</t>
+          <t>582465</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1557874</t>
+          <t>1560150</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1628982</t>
+          <t>1624430</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,19%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37080</t>
+          <t>37229</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>62618</t>
+          <t>62935</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>131848</t>
+          <t>132989</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>174746</t>
+          <t>174774</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>179672</t>
+          <t>177163</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>232771</t>
+          <t>228527</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>24,89%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>286919</t>
+          <t>286602</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>312457</t>
+          <t>312308</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>394006</t>
+          <t>393978</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>436904</t>
+          <t>435763</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>685518</t>
+          <t>689762</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>738617</t>
+          <t>741126</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,71%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11656</t>
+          <t>10800</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27200</t>
+          <t>27558</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>281788</t>
+          <t>280983</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>343036</t>
+          <t>344320</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>298510</t>
+          <t>298604</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>362198</t>
+          <t>362786</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,45%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>271001</t>
+          <t>270643</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>286545</t>
+          <t>287401</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>905724</t>
+          <t>904440</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>966972</t>
+          <t>967777</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1184762</t>
+          <t>1184174</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1248450</t>
+          <t>1248356</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>415575</t>
+          <t>417754</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>493671</t>
+          <t>498621</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>758649</t>
+          <t>760035</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>858134</t>
+          <t>856955</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1197307</t>
+          <t>1205893</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1326977</t>
+          <t>1331391</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,03%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2775501</t>
+          <t>2770551</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2853597</t>
+          <t>2851418</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2519990</t>
+          <t>2521169</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2619475</t>
+          <t>2618089</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5320319</t>
+          <t>5315905</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5449989</t>
+          <t>5441403</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,86%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42593</t>
+          <t>42798</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>72608</t>
+          <t>71682</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>65759</t>
+          <t>65694</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>98580</t>
+          <t>97791</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>117797</t>
+          <t>118304</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>159131</t>
+          <t>159548</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,23%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>364603</t>
+          <t>365529</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>394618</t>
+          <t>394413</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>215874</t>
+          <t>216663</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>248695</t>
+          <t>248760</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>592534</t>
+          <t>592117</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>633868</t>
+          <t>633361</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,26%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60203</t>
+          <t>60663</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>94021</t>
+          <t>94311</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>91165</t>
+          <t>90577</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>126353</t>
+          <t>128189</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>159076</t>
+          <t>158701</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>208702</t>
+          <t>207919</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,57%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>322997</t>
+          <t>322707</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>356815</t>
+          <t>356355</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>210681</t>
+          <t>208845</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>245869</t>
+          <t>246457</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>545350</t>
+          <t>546133</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>594976</t>
+          <t>595351</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>78,95%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>111675</t>
+          <t>111980</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>154987</t>
+          <t>157171</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58597</t>
+          <t>59205</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88798</t>
+          <t>89770</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>179757</t>
+          <t>181893</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>233915</t>
+          <t>235632</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>473342</t>
+          <t>471158</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>516654</t>
+          <t>516349</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>169140</t>
+          <t>168168</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>199341</t>
+          <t>198733</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>652352</t>
+          <t>650635</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>706510</t>
+          <t>704374</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,48%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>209181</t>
+          <t>207695</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>265148</t>
+          <t>262213</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>205966</t>
+          <t>205827</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>255148</t>
+          <t>257576</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>431849</t>
+          <t>427775</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>505289</t>
+          <t>505519</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,27%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>892167</t>
+          <t>895102</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>948134</t>
+          <t>949620</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>511509</t>
+          <t>509081</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>560691</t>
+          <t>560830</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1418684</t>
+          <t>1418454</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1492124</t>
+          <t>1496198</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,77%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>74729</t>
+          <t>75696</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>110040</t>
+          <t>108084</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>264192</t>
+          <t>263484</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>320390</t>
+          <t>317460</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>348663</t>
+          <t>350772</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>415332</t>
+          <t>419184</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,98%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>400556</t>
+          <t>402512</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>435867</t>
+          <t>434900</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>440097</t>
+          <t>443027</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>496295</t>
+          <t>497003</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>855752</t>
+          <t>851900</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>922421</t>
+          <t>920312</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,4%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12292</t>
+          <t>12050</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27720</t>
+          <t>28072</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>368787</t>
+          <t>369132</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>435593</t>
+          <t>431611</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>386883</t>
+          <t>387621</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>457993</t>
+          <t>459346</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,48%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>238121</t>
+          <t>237769</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>253549</t>
+          <t>253791</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>670647</t>
+          <t>674629</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>737453</t>
+          <t>737108</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>914088</t>
+          <t>912735</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>985198</t>
+          <t>984460</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,75%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>565363</t>
+          <t>568332</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>658090</t>
+          <t>655853</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1125788</t>
+          <t>1130887</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1243950</t>
+          <t>1247010</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1721812</t>
+          <t>1727177</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1870194</t>
+          <t>1876322</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,96%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2758220</t>
+          <t>2760457</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2850947</t>
+          <t>2847978</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2298861</t>
+          <t>2295801</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2417023</t>
+          <t>2411924</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5088927</t>
+          <t>5082799</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5237309</t>
+          <t>5231944</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>75,18%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>68462</t>
+          <t>69278</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>102693</t>
+          <t>101540</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>67348</t>
+          <t>67886</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>98345</t>
+          <t>99112</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>141390</t>
+          <t>144182</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>189395</t>
+          <t>191485</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,67%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>326399</t>
+          <t>327552</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>360630</t>
+          <t>359814</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>248710</t>
+          <t>247943</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>279707</t>
+          <t>279169</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>586752</t>
+          <t>584662</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>634757</t>
+          <t>631965</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,42%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52927</t>
+          <t>51205</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82256</t>
+          <t>82195</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>80776</t>
+          <t>77920</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>114848</t>
+          <t>114360</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>139244</t>
+          <t>141086</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>186305</t>
+          <t>185503</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>294971</t>
+          <t>295032</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>324300</t>
+          <t>326022</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>257425</t>
+          <t>257913</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>291497</t>
+          <t>294353</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>563195</t>
+          <t>563997</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>610256</t>
+          <t>608414</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,18%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>86964</t>
+          <t>86325</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>123248</t>
+          <t>122198</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46897</t>
+          <t>46894</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73681</t>
+          <t>72758</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>142797</t>
+          <t>142226</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>188660</t>
+          <t>186623</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,12%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>398666</t>
+          <t>399716</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>434950</t>
+          <t>435589</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92442</t>
+          <t>93365</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>119226</t>
+          <t>119229</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>499376</t>
+          <t>501413</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>545239</t>
+          <t>545810</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>79,33%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>200283</t>
+          <t>202224</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>257768</t>
+          <t>257476</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>213813</t>
+          <t>210817</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>264417</t>
+          <t>266713</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>429790</t>
+          <t>428635</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>509965</t>
+          <t>505969</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,61%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>891870</t>
+          <t>892162</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>949355</t>
+          <t>947414</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>561459</t>
+          <t>559163</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>612063</t>
+          <t>615059</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1465549</t>
+          <t>1469545</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1545724</t>
+          <t>1546879</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,3%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>97368</t>
+          <t>98706</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>137398</t>
+          <t>134734</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>240520</t>
+          <t>239916</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>291230</t>
+          <t>291887</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>346793</t>
+          <t>350197</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>414600</t>
+          <t>415392</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,57%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>483308</t>
+          <t>485972</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>523338</t>
+          <t>522000</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>447014</t>
+          <t>446357</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>497724</t>
+          <t>498328</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>944350</t>
+          <t>943558</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1012157</t>
+          <t>1008753</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,23%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26618</t>
+          <t>26045</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>51518</t>
+          <t>50677</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>325245</t>
+          <t>324833</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>388116</t>
+          <t>384888</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>361204</t>
+          <t>356725</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>428615</t>
+          <t>427184</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,2%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>235627</t>
+          <t>236468</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260527</t>
+          <t>261100</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>693909</t>
+          <t>697137</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>756780</t>
+          <t>757192</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>940555</t>
+          <t>941986</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1007966</t>
+          <t>1012445</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,95%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>590418</t>
+          <t>591144</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>681638</t>
+          <t>686530</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1038332</t>
+          <t>1030494</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1157172</t>
+          <t>1149512</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1663220</t>
+          <t>1666324</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1808228</t>
+          <t>1808375</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2704084</t>
+          <t>2699192</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2795304</t>
+          <t>2794578</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2374424</t>
+          <t>2382084</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2493264</t>
+          <t>2501102</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5109090</t>
+          <t>5108943</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5254098</t>
+          <t>5250994</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8264,7 +8264,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,91%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>94244</t>
+          <t>107558</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>76905</t>
+          <t>90155</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>115335</t>
+          <t>128427</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>143254</t>
+          <t>152673</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>125733</t>
+          <t>134800</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>160615</t>
+          <t>168444</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>237498</t>
+          <t>260231</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>213122</t>
+          <t>233068</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>264221</t>
+          <t>284379</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,37%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>410968</t>
+          <t>443060</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>389877</t>
+          <t>422191</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>428307</t>
+          <t>460463</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>304213</t>
+          <t>335738</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>286852</t>
+          <t>319967</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>321734</t>
+          <t>353611</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>715181</t>
+          <t>778798</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>688458</t>
+          <t>754650</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>739557</t>
+          <t>805961</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,57%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>93446</t>
+          <t>95336</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>76881</t>
+          <t>78921</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>111643</t>
+          <t>113792</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>122005</t>
+          <t>133481</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>106927</t>
+          <t>117615</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>138636</t>
+          <t>151172</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>215451</t>
+          <t>228817</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>193854</t>
+          <t>205903</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>238291</t>
+          <t>254722</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,1%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>358767</t>
+          <t>387876</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>340570</t>
+          <t>369420</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>375332</t>
+          <t>404291</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>260575</t>
+          <t>289662</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>243944</t>
+          <t>271971</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>275653</t>
+          <t>305528</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>619342</t>
+          <t>677538</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>596502</t>
+          <t>651633</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>640939</t>
+          <t>700452</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>77,28%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>117832</t>
+          <t>130750</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47991</t>
+          <t>111072</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>195026</t>
+          <t>151842</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>78878</t>
+          <t>87361</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>68438</t>
+          <t>75884</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89012</t>
+          <t>100159</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>196710</t>
+          <t>218111</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>92097</t>
+          <t>194808</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>285635</t>
+          <t>241120</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>36,58%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>550432</t>
+          <t>340862</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>473238</t>
+          <t>319770</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>620273</t>
+          <t>360540</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>88033</t>
+          <t>100136</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>77899</t>
+          <t>87338</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>98473</t>
+          <t>111613</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>53,41%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>638465</t>
+          <t>440998</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>549540</t>
+          <t>417989</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>743078</t>
+          <t>464301</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>70,44%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>297376</t>
+          <t>320654</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>266931</t>
+          <t>289938</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>330128</t>
+          <t>352879</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>505168</t>
+          <t>335075</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>369053</t>
+          <t>309657</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>695500</t>
+          <t>358529</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>802544</t>
+          <t>655728</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>650127</t>
+          <t>616887</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1195798</t>
+          <t>699698</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>35,11%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>737443</t>
+          <t>811189</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>704691</t>
+          <t>778964</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>767888</t>
+          <t>841905</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>472926</t>
+          <t>526136</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>282594</t>
+          <t>502682</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>609041</t>
+          <t>551554</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1210368</t>
+          <t>1337326</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>817114</t>
+          <t>1293356</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1362785</t>
+          <t>1376167</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>69,05%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>129047</t>
+          <t>143733</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>110249</t>
+          <t>122505</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>150591</t>
+          <t>167212</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>365777</t>
+          <t>398331</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>278410</t>
+          <t>374454</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>418190</t>
+          <t>421292</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>494823</t>
+          <t>542064</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>400405</t>
+          <t>507156</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>543791</t>
+          <t>576286</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,22%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>345999</t>
+          <t>424231</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>324455</t>
+          <t>400752</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>364797</t>
+          <t>445459</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>473219</t>
+          <t>431796</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>420806</t>
+          <t>408835</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>560586</t>
+          <t>455673</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>52,02%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>819218</t>
+          <t>856027</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>770250</t>
+          <t>821805</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>913636</t>
+          <t>890935</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>63,73%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1314041</t>
+          <t>1398091</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1314041</t>
+          <t>1398091</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1314041</t>
+          <t>1398091</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>31244</t>
+          <t>26333</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17749</t>
+          <t>14183</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>55648</t>
+          <t>44130</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>292731</t>
+          <t>317005</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>269898</t>
+          <t>289265</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>316226</t>
+          <t>342450</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>323975</t>
+          <t>343338</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>292633</t>
+          <t>312082</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>354209</t>
+          <t>375803</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>34,79%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>209263</t>
+          <t>210895</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>184859</t>
+          <t>193098</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>222758</t>
+          <t>223045</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>467421</t>
+          <t>525988</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>443926</t>
+          <t>500543</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>490254</t>
+          <t>553728</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>676684</t>
+          <t>736883</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>646450</t>
+          <t>704418</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>708026</t>
+          <t>768139</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>71,11%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>763190</t>
+          <t>824363</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>597696</t>
+          <t>771100</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>842135</t>
+          <t>878557</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1507812</t>
+          <t>1423927</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1356729</t>
+          <t>1374304</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1900198</t>
+          <t>1476599</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2271002</t>
+          <t>2248290</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2029388</t>
+          <t>2174686</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2720438</t>
+          <t>2324235</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>32,85%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2612870</t>
+          <t>2618113</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2533925</t>
+          <t>2563919</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2778364</t>
+          <t>2671376</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2066387</t>
+          <t>2209455</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1674001</t>
+          <t>2156783</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2217470</t>
+          <t>2259078</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>4679258</t>
+          <t>4827568</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4229822</t>
+          <t>4751623</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4920872</t>
+          <t>4901172</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>69,27%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3574199</t>
+          <t>3633382</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3574199</t>
+          <t>3633382</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3574199</t>
+          <t>3633382</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6950260</t>
+          <t>7075858</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6950260</t>
+          <t>7075858</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6950260</t>
+          <t>7075858</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
